--- a/BSCS_2Year_A_COR.xlsx
+++ b/BSCS_2Year_A_COR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\PDFonly\revised_data_proc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\a\GROUP-3-AI-collab-nice-main\GROUP-3-AI-collab-nice-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85652AEE-A2E4-4418-9707-D31E93CA4CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5165B76D-4FC8-4B8E-8B79-CD9024616917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificate of Registration" sheetId="1" r:id="rId1"/>
